--- a/docs/reports/Shelly_Roster_Labour.xlsx
+++ b/docs/reports/Shelly_Roster_Labour.xlsx
@@ -590,7 +590,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Forecast sales" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="2022.63" maxValue="24015.31"/>
+      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="1985.41" maxValue="24015.31"/>
     </cacheField>
   </cacheFields>
 </pivotCacheDefinition>
@@ -601,52 +601,52 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="2369.78"/>
+    <n v="2373.37"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
-    <n v="2022.63"/>
+    <n v="1985.41"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
-    <n v="2777.23"/>
+    <n v="2827.57"/>
   </r>
   <r>
     <x v="3"/>
     <x v="0"/>
-    <n v="2931.02"/>
+    <n v="2925.14"/>
   </r>
   <r>
     <x v="4"/>
     <x v="0"/>
-    <n v="2943.15"/>
+    <n v="2949.26"/>
   </r>
   <r>
     <x v="5"/>
     <x v="0"/>
-    <n v="2990.31"/>
+    <n v="3000.51"/>
   </r>
   <r>
     <x v="6"/>
     <x v="0"/>
-    <n v="3040.89"/>
+    <n v="3040.16"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="19075"/>
+    <n v="19101.43"/>
   </r>
   <r>
     <x v="7"/>
     <x v="1"/>
-    <n v="19744.73"/>
+    <n v="19763.97"/>
   </r>
   <r>
     <x v="8"/>
     <x v="1"/>
-    <n v="19580.27"/>
+    <n v="19587.54"/>
   </r>
   <r>
     <x v="9"/>
@@ -1170,22 +1170,22 @@
     <row r="10">
       <c r="B10" s="10">
         <f>Model!$D$15</f>
-        <v>181.478181818182</v>
+        <v>182.024</v>
       </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="11">
         <f>Model!$E$15</f>
-        <v>4899.91090909091</v>
+        <v>4914.648</v>
       </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="12">
         <f>Model!$F$15</f>
-        <v>0.256875928719875</v>
+        <v>0.257292285076188</v>
       </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="11">
         <f>Model!$E$34</f>
-        <v>67686.354</v>
+        <v>67699.3483636364</v>
       </c>
       <c r="M10" s="9" t="n"/>
     </row>
@@ -1216,12 +1216,12 @@
     <row r="14">
       <c r="B14" s="10">
         <f>Model!$D$34</f>
-        <v>2506.902</v>
+        <v>2507.38327272727</v>
       </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="10">
         <f>Model!$G$34</f>
-        <v>4.82096538461539</v>
+        <v>4.82189090909091</v>
       </c>
       <c r="G14" s="9" t="n"/>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C8" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B8)</f>
-        <v>2369.78</v>
+        <v>2373.37</v>
       </c>
       <c r="D8" s="17">
         <f>MAX(Assumptions!$C$7,C8/Assumptions!$C$6)</f>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F8" s="18">
         <f>IFERROR(E8/C8,0)</f>
-        <v>0.273443104423195</v>
+        <v>0.27302948971294</v>
       </c>
       <c r="G8" s="19">
         <f>ROUNDUP(D8/8,0)</f>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C9" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B9)</f>
-        <v>2022.63</v>
+        <v>1985.41</v>
       </c>
       <c r="D9" s="17">
         <f>MAX(Assumptions!$C$7,C9/Assumptions!$C$6)</f>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F9" s="18">
         <f>IFERROR(E9/C9,0)</f>
-        <v>0.3203749573575</v>
+        <v>0.326380949023124</v>
       </c>
       <c r="G9" s="19">
         <f>ROUNDUP(D9/8,0)</f>
@@ -1439,15 +1439,15 @@
       </c>
       <c r="C10" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B10)</f>
-        <v>2777.23</v>
+        <v>2827.57</v>
       </c>
       <c r="D10" s="17">
         <f>MAX(Assumptions!$C$7,C10/Assumptions!$C$6)</f>
-        <v>25.2475454545455</v>
+        <v>25.7051818181818</v>
       </c>
       <c r="E10" s="16">
         <f>D10*Assumptions!$C$8</f>
-        <v>681.683727272727</v>
+        <v>694.039909090909</v>
       </c>
       <c r="F10" s="18">
         <f>IFERROR(E10/C10,0)</f>
@@ -1464,15 +1464,15 @@
       </c>
       <c r="C11" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B11)</f>
-        <v>2931.02</v>
+        <v>2925.14</v>
       </c>
       <c r="D11" s="17">
         <f>MAX(Assumptions!$C$7,C11/Assumptions!$C$6)</f>
-        <v>26.6456363636364</v>
+        <v>26.5921818181818</v>
       </c>
       <c r="E11" s="16">
         <f>D11*Assumptions!$C$8</f>
-        <v>719.432181818182</v>
+        <v>717.988909090909</v>
       </c>
       <c r="F11" s="18">
         <f>IFERROR(E11/C11,0)</f>
@@ -1489,15 +1489,15 @@
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B12)</f>
-        <v>2943.15</v>
+        <v>2949.26</v>
       </c>
       <c r="D12" s="17">
         <f>MAX(Assumptions!$C$7,C12/Assumptions!$C$6)</f>
-        <v>26.7559090909091</v>
+        <v>26.8114545454546</v>
       </c>
       <c r="E12" s="16">
         <f>D12*Assumptions!$C$8</f>
-        <v>722.409545454546</v>
+        <v>723.909272727273</v>
       </c>
       <c r="F12" s="18">
         <f>IFERROR(E12/C12,0)</f>
@@ -1514,15 +1514,15 @@
       </c>
       <c r="C13" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B13)</f>
-        <v>2990.31</v>
+        <v>3000.51</v>
       </c>
       <c r="D13" s="17">
         <f>MAX(Assumptions!$C$7,C13/Assumptions!$C$6)</f>
-        <v>27.1846363636364</v>
+        <v>27.2773636363636</v>
       </c>
       <c r="E13" s="16">
         <f>D13*Assumptions!$C$8</f>
-        <v>733.985181818182</v>
+        <v>736.488818181818</v>
       </c>
       <c r="F13" s="18">
         <f>IFERROR(E13/C13,0)</f>
@@ -1539,15 +1539,15 @@
       </c>
       <c r="C14" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B14)</f>
-        <v>3040.89</v>
+        <v>3040.16</v>
       </c>
       <c r="D14" s="17">
         <f>MAX(Assumptions!$C$7,C14/Assumptions!$C$6)</f>
-        <v>27.6444545454545</v>
+        <v>27.6378181818182</v>
       </c>
       <c r="E14" s="16">
         <f>D14*Assumptions!$C$8</f>
-        <v>746.400272727273</v>
+        <v>746.221090909091</v>
       </c>
       <c r="F14" s="18">
         <f>IFERROR(E14/C14,0)</f>
@@ -1566,19 +1566,19 @@
       </c>
       <c r="C15" s="21">
         <f>SUM(C8:C14)</f>
-        <v>19075.01</v>
+        <v>19101.42</v>
       </c>
       <c r="D15" s="22">
         <f>SUM(D8:D14)</f>
-        <v>181.478181818182</v>
+        <v>182.024</v>
       </c>
       <c r="E15" s="21">
         <f>SUM(E8:E14)</f>
-        <v>4899.91090909091</v>
+        <v>4914.648</v>
       </c>
       <c r="F15" s="23">
         <f>IFERROR(E15/C15,0)</f>
-        <v>0.256875928719875</v>
+        <v>0.257292285076188</v>
       </c>
       <c r="G15" s="24">
         <f>SUM(G8:G14)</f>
@@ -1630,15 +1630,15 @@
       </c>
       <c r="C21" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B21)</f>
-        <v>19075</v>
+        <v>19101.43</v>
       </c>
       <c r="D21" s="17">
         <f>MAX(Assumptions!$C$7*7,C21/Assumptions!$C$6)</f>
-        <v>173.409090909091</v>
+        <v>173.649363636364</v>
       </c>
       <c r="E21" s="16">
         <f>D21*Assumptions!$C$8</f>
-        <v>4682.04545454545</v>
+        <v>4688.53281818182</v>
       </c>
       <c r="F21" s="18">
         <f>IFERROR(E21/C21,0)</f>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G21" s="17">
         <f>D21/40</f>
-        <v>4.33522727272727</v>
+        <v>4.34123409090909</v>
       </c>
     </row>
     <row r="22">
@@ -1655,15 +1655,15 @@
       </c>
       <c r="C22" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B22)</f>
-        <v>19744.73</v>
+        <v>19763.97</v>
       </c>
       <c r="D22" s="17">
         <f>MAX(Assumptions!$C$7*7,C22/Assumptions!$C$6)</f>
-        <v>179.497545454545</v>
+        <v>179.672454545455</v>
       </c>
       <c r="E22" s="16">
         <f>D22*Assumptions!$C$8</f>
-        <v>4846.43372727273</v>
+        <v>4851.15627272727</v>
       </c>
       <c r="F22" s="18">
         <f>IFERROR(E22/C22,0)</f>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="G22" s="17">
         <f>D22/40</f>
-        <v>4.48743863636364</v>
+        <v>4.49181136363636</v>
       </c>
     </row>
     <row r="23">
@@ -1680,15 +1680,15 @@
       </c>
       <c r="C23" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B23)</f>
-        <v>19580.27</v>
+        <v>19587.54</v>
       </c>
       <c r="D23" s="17">
         <f>MAX(Assumptions!$C$7*7,C23/Assumptions!$C$6)</f>
-        <v>178.002454545455</v>
+        <v>178.068545454545</v>
       </c>
       <c r="E23" s="16">
         <f>D23*Assumptions!$C$8</f>
-        <v>4806.06627272727</v>
+        <v>4807.85072727273</v>
       </c>
       <c r="F23" s="18">
         <f>IFERROR(E23/C23,0)</f>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G23" s="17">
         <f>D23/40</f>
-        <v>4.45006136363636</v>
+        <v>4.45171363636364</v>
       </c>
     </row>
     <row r="24">
@@ -1957,23 +1957,23 @@
       </c>
       <c r="C34" s="21">
         <f>SUM(C21:C33)</f>
-        <v>275759.22</v>
+        <v>275812.16</v>
       </c>
       <c r="D34" s="22">
         <f>SUM(D21:D33)</f>
-        <v>2506.902</v>
+        <v>2507.38327272727</v>
       </c>
       <c r="E34" s="21">
         <f>SUM(E21:E33)</f>
-        <v>67686.354</v>
+        <v>67699.3483636364</v>
       </c>
       <c r="F34" s="23">
         <f>IFERROR(E34/C34,0)</f>
-        <v>0.245454545454546</v>
+        <v>0.245454545454545</v>
       </c>
       <c r="G34" s="22">
         <f>IFERROR(AVERAGE(G21:G33),0)</f>
-        <v>4.82096538461539</v>
+        <v>4.82189090909091</v>
       </c>
     </row>
   </sheetData>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B7" s="25" t="n">
-        <v>19075.01</v>
+        <v>19101.42</v>
       </c>
     </row>
     <row r="8">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="B8" s="25" t="n">
-        <v>275759.22</v>
+        <v>275812.16</v>
       </c>
     </row>
     <row r="9">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>294834.23</v>
+        <v>294913.58</v>
       </c>
     </row>
   </sheetData>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="C2" s="29" t="n">
-        <v>2369.78</v>
+        <v>2373.37</v>
       </c>
     </row>
     <row r="3">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="C3" s="29" t="n">
-        <v>2022.63</v>
+        <v>1985.41</v>
       </c>
     </row>
     <row r="4">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>2777.23</v>
+        <v>2827.57</v>
       </c>
     </row>
     <row r="5">
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C5" s="29" t="n">
-        <v>2931.02</v>
+        <v>2925.14</v>
       </c>
     </row>
     <row r="6">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>2943.15</v>
+        <v>2949.26</v>
       </c>
     </row>
     <row r="7">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>2990.31</v>
+        <v>3000.51</v>
       </c>
     </row>
     <row r="8">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>3040.89</v>
+        <v>3040.16</v>
       </c>
     </row>
     <row r="9">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>19075</v>
+        <v>19101.43</v>
       </c>
     </row>
     <row r="10">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="C10" s="29" t="n">
-        <v>19744.73</v>
+        <v>19763.97</v>
       </c>
     </row>
     <row r="11">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C11" s="29" t="n">
-        <v>19580.27</v>
+        <v>19587.54</v>
       </c>
     </row>
     <row r="12">
@@ -2667,7 +2667,7 @@
     <row r="6">
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.1.0.</t>
+          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.4.0.</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 29 Sep 2026 22:17</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Roster_Labour.xlsx
+++ b/docs/reports/Shelly_Roster_Labour.xlsx
@@ -2771,7 +2771,7 @@
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:51</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Roster_Labour.xlsx
+++ b/docs/reports/Shelly_Roster_Labour.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookup" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pivot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lookup" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="in_splh">Assumptions!$C$6</definedName>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
   <pivotCaches>
-    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -313,13 +313,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -341,10 +341,10 @@
             <v>Hours</v>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A8FB8"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="2A8FB8"/>
               </a:solidFill>
@@ -402,13 +402,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -430,10 +430,10 @@
             <v>Hours</v>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A8FB8"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="2A8FB8"/>
               </a:solidFill>
@@ -506,7 +506,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -521,9 +521,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -543,9 +543,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -562,25 +562,25 @@
   <cacheFields count="3">
     <cacheField name="Date" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
       <sharedItems count="19">
-        <s v="2026-09-26"/>
-        <s v="2026-09-27"/>
-        <s v="2026-09-28"/>
-        <s v="2026-09-29"/>
-        <s v="2026-09-30"/>
-        <s v="2026-10-01"/>
-        <s v="2026-10-02"/>
-        <s v="2026-10-03"/>
+        <s v="2026-10-05"/>
+        <s v="2026-10-06"/>
+        <s v="2026-10-07"/>
+        <s v="2026-10-08"/>
+        <s v="2026-10-09"/>
         <s v="2026-10-10"/>
-        <s v="2026-10-17"/>
-        <s v="2026-10-24"/>
-        <s v="2026-10-31"/>
-        <s v="2026-11-07"/>
-        <s v="2026-11-14"/>
-        <s v="2026-11-21"/>
-        <s v="2026-11-28"/>
-        <s v="2026-12-05"/>
-        <s v="2026-12-12"/>
-        <s v="2026-12-19"/>
+        <s v="2026-10-11"/>
+        <s v="2026-10-12"/>
+        <s v="2026-10-19"/>
+        <s v="2026-10-26"/>
+        <s v="2026-11-02"/>
+        <s v="2026-11-09"/>
+        <s v="2026-11-16"/>
+        <s v="2026-11-23"/>
+        <s v="2026-11-30"/>
+        <s v="2026-12-07"/>
+        <s v="2026-12-14"/>
+        <s v="2026-12-21"/>
+        <s v="2026-12-28"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Type" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
@@ -590,7 +590,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Forecast sales" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="1985.41" maxValue="24015.31"/>
+      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="2102.99" maxValue="23828.14"/>
     </cacheField>
   </cacheFields>
 </pivotCacheDefinition>
@@ -601,102 +601,102 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="2373.37"/>
+    <n v="2953.86"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
-    <n v="1985.41"/>
+    <n v="2940.45"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
-    <n v="2827.57"/>
+    <n v="2986.75"/>
   </r>
   <r>
     <x v="3"/>
     <x v="0"/>
-    <n v="2925.14"/>
+    <n v="2963.84"/>
   </r>
   <r>
     <x v="4"/>
     <x v="0"/>
-    <n v="2949.26"/>
+    <n v="3040.24"/>
   </r>
   <r>
     <x v="5"/>
     <x v="0"/>
-    <n v="3000.51"/>
+    <n v="2360.41"/>
   </r>
   <r>
     <x v="6"/>
     <x v="0"/>
-    <n v="3040.16"/>
+    <n v="2102.99"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="19101.43"/>
+    <n v="19348.54"/>
   </r>
   <r>
     <x v="7"/>
     <x v="1"/>
-    <n v="19763.97"/>
+    <n v="19657.87"/>
   </r>
   <r>
     <x v="8"/>
     <x v="1"/>
-    <n v="19587.54"/>
+    <n v="20336.76"/>
   </r>
   <r>
     <x v="9"/>
     <x v="1"/>
-    <n v="19999.31"/>
+    <n v="19047.27"/>
   </r>
   <r>
     <x v="10"/>
     <x v="1"/>
-    <n v="20093.27"/>
+    <n v="21468.36"/>
   </r>
   <r>
     <x v="11"/>
     <x v="1"/>
-    <n v="20478.63"/>
+    <n v="21326.85"/>
   </r>
   <r>
     <x v="12"/>
     <x v="1"/>
-    <n v="21381.07"/>
+    <n v="21203.71"/>
   </r>
   <r>
     <x v="13"/>
     <x v="1"/>
-    <n v="21226.65"/>
+    <n v="21889.32"/>
   </r>
   <r>
     <x v="14"/>
     <x v="1"/>
-    <n v="21515.39"/>
+    <n v="23828.14"/>
   </r>
   <r>
     <x v="15"/>
     <x v="1"/>
-    <n v="22912.01"/>
+    <n v="23146.13"/>
   </r>
   <r>
     <x v="16"/>
     <x v="1"/>
-    <n v="23487.6"/>
+    <n v="23704.91"/>
   </r>
   <r>
     <x v="17"/>
     <x v="1"/>
-    <n v="24015.31"/>
+    <n v="21888.02"/>
   </r>
   <r>
     <x v="18"/>
     <x v="1"/>
-    <n v="22249.98"/>
+    <n v="19071.55"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -1104,7 +1104,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Demo Neighbourhood Store (Eden Terrace format) · from 26 Sep 2026</t>
+          <t>Demo Neighbourhood Store (Eden Terrace format) · from 05 Oct 2026</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1170,22 +1170,22 @@
     <row r="10">
       <c r="B10" s="10">
         <f>Model!$D$15</f>
-        <v>182.024</v>
+        <v>183.319454545455</v>
       </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="11">
         <f>Model!$E$15</f>
-        <v>4914.648</v>
+        <v>4949.62527272727</v>
       </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="12">
         <f>Model!$F$15</f>
-        <v>0.257292285076188</v>
+        <v>0.255813889457668</v>
       </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="11">
         <f>Model!$E$34</f>
-        <v>67699.3483636364</v>
+        <v>67725.1873636364</v>
       </c>
       <c r="M10" s="9" t="n"/>
     </row>
@@ -1216,12 +1216,12 @@
     <row r="14">
       <c r="B14" s="10">
         <f>Model!$D$34</f>
-        <v>2507.38327272727</v>
+        <v>2508.34027272727</v>
       </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="10">
         <f>Model!$G$34</f>
-        <v>4.82189090909091</v>
+        <v>4.82373129370629</v>
       </c>
       <c r="G14" s="9" t="n"/>
     </row>
@@ -1385,69 +1385,69 @@
     </row>
     <row r="8">
       <c r="B8" s="15" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C8" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B8)</f>
-        <v>2373.37</v>
+        <v>2953.86</v>
       </c>
       <c r="D8" s="17">
         <f>MAX(Assumptions!$C$7,C8/Assumptions!$C$6)</f>
-        <v>24</v>
+        <v>26.8532727272727</v>
       </c>
       <c r="E8" s="16">
         <f>D8*Assumptions!$C$8</f>
-        <v>648</v>
+        <v>725.038363636364</v>
       </c>
       <c r="F8" s="18">
         <f>IFERROR(E8/C8,0)</f>
-        <v>0.27302948971294</v>
+        <v>0.245454545454545</v>
       </c>
       <c r="G8" s="19">
         <f>ROUNDUP(D8/8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="15" t="n">
-        <v>46292</v>
+        <v>46301</v>
       </c>
       <c r="C9" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B9)</f>
-        <v>1985.41</v>
+        <v>2940.45</v>
       </c>
       <c r="D9" s="17">
         <f>MAX(Assumptions!$C$7,C9/Assumptions!$C$6)</f>
-        <v>24</v>
+        <v>26.7313636363636</v>
       </c>
       <c r="E9" s="16">
         <f>D9*Assumptions!$C$8</f>
-        <v>648</v>
+        <v>721.746818181818</v>
       </c>
       <c r="F9" s="18">
         <f>IFERROR(E9/C9,0)</f>
-        <v>0.326380949023124</v>
+        <v>0.245454545454545</v>
       </c>
       <c r="G9" s="19">
         <f>ROUNDUP(D9/8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="15" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="C10" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B10)</f>
-        <v>2827.57</v>
+        <v>2986.75</v>
       </c>
       <c r="D10" s="17">
         <f>MAX(Assumptions!$C$7,C10/Assumptions!$C$6)</f>
-        <v>25.7051818181818</v>
+        <v>27.1522727272727</v>
       </c>
       <c r="E10" s="16">
         <f>D10*Assumptions!$C$8</f>
-        <v>694.039909090909</v>
+        <v>733.111363636364</v>
       </c>
       <c r="F10" s="18">
         <f>IFERROR(E10/C10,0)</f>
@@ -1460,19 +1460,19 @@
     </row>
     <row r="11">
       <c r="B11" s="15" t="n">
-        <v>46294</v>
+        <v>46303</v>
       </c>
       <c r="C11" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B11)</f>
-        <v>2925.14</v>
+        <v>2963.84</v>
       </c>
       <c r="D11" s="17">
         <f>MAX(Assumptions!$C$7,C11/Assumptions!$C$6)</f>
-        <v>26.5921818181818</v>
+        <v>26.944</v>
       </c>
       <c r="E11" s="16">
         <f>D11*Assumptions!$C$8</f>
-        <v>717.988909090909</v>
+        <v>727.488</v>
       </c>
       <c r="F11" s="18">
         <f>IFERROR(E11/C11,0)</f>
@@ -1485,19 +1485,19 @@
     </row>
     <row r="12">
       <c r="B12" s="15" t="n">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B12)</f>
-        <v>2949.26</v>
+        <v>3040.24</v>
       </c>
       <c r="D12" s="17">
         <f>MAX(Assumptions!$C$7,C12/Assumptions!$C$6)</f>
-        <v>26.8114545454546</v>
+        <v>27.6385454545455</v>
       </c>
       <c r="E12" s="16">
         <f>D12*Assumptions!$C$8</f>
-        <v>723.909272727273</v>
+        <v>746.240727272727</v>
       </c>
       <c r="F12" s="18">
         <f>IFERROR(E12/C12,0)</f>
@@ -1510,52 +1510,52 @@
     </row>
     <row r="13">
       <c r="B13" s="15" t="n">
-        <v>46296</v>
+        <v>46305</v>
       </c>
       <c r="C13" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B13)</f>
-        <v>3000.51</v>
+        <v>2360.41</v>
       </c>
       <c r="D13" s="17">
         <f>MAX(Assumptions!$C$7,C13/Assumptions!$C$6)</f>
-        <v>27.2773636363636</v>
+        <v>24</v>
       </c>
       <c r="E13" s="16">
         <f>D13*Assumptions!$C$8</f>
-        <v>736.488818181818</v>
+        <v>648</v>
       </c>
       <c r="F13" s="18">
         <f>IFERROR(E13/C13,0)</f>
-        <v>0.245454545454545</v>
+        <v>0.274528577662355</v>
       </c>
       <c r="G13" s="19">
         <f>ROUNDUP(D13/8,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="15" t="n">
-        <v>46297</v>
+        <v>46306</v>
       </c>
       <c r="C14" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B14)</f>
-        <v>3040.16</v>
+        <v>2102.99</v>
       </c>
       <c r="D14" s="17">
         <f>MAX(Assumptions!$C$7,C14/Assumptions!$C$6)</f>
-        <v>27.6378181818182</v>
+        <v>24</v>
       </c>
       <c r="E14" s="16">
         <f>D14*Assumptions!$C$8</f>
-        <v>746.221090909091</v>
+        <v>648</v>
       </c>
       <c r="F14" s="18">
         <f>IFERROR(E14/C14,0)</f>
-        <v>0.245454545454545</v>
+        <v>0.308132706289616</v>
       </c>
       <c r="G14" s="19">
         <f>ROUNDUP(D14/8,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1566,19 +1566,19 @@
       </c>
       <c r="C15" s="21">
         <f>SUM(C8:C14)</f>
-        <v>19101.42</v>
+        <v>19348.54</v>
       </c>
       <c r="D15" s="22">
         <f>SUM(D8:D14)</f>
-        <v>182.024</v>
+        <v>183.319454545455</v>
       </c>
       <c r="E15" s="21">
         <f>SUM(E8:E14)</f>
-        <v>4914.648</v>
+        <v>4949.62527272727</v>
       </c>
       <c r="F15" s="23">
         <f>IFERROR(E15/C15,0)</f>
-        <v>0.257292285076188</v>
+        <v>0.255813889457668</v>
       </c>
       <c r="G15" s="24">
         <f>SUM(G8:G14)</f>
@@ -1626,19 +1626,19 @@
     </row>
     <row r="21">
       <c r="B21" s="15" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="C21" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B21)</f>
-        <v>19101.43</v>
+        <v>19348.54</v>
       </c>
       <c r="D21" s="17">
         <f>MAX(Assumptions!$C$7*7,C21/Assumptions!$C$6)</f>
-        <v>173.649363636364</v>
+        <v>175.895818181818</v>
       </c>
       <c r="E21" s="16">
         <f>D21*Assumptions!$C$8</f>
-        <v>4688.53281818182</v>
+        <v>4749.18709090909</v>
       </c>
       <c r="F21" s="18">
         <f>IFERROR(E21/C21,0)</f>
@@ -1646,24 +1646,24 @@
       </c>
       <c r="G21" s="17">
         <f>D21/40</f>
-        <v>4.34123409090909</v>
+        <v>4.39739545454546</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="15" t="n">
-        <v>46298</v>
+        <v>46307</v>
       </c>
       <c r="C22" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B22)</f>
-        <v>19763.97</v>
+        <v>19657.87</v>
       </c>
       <c r="D22" s="17">
         <f>MAX(Assumptions!$C$7*7,C22/Assumptions!$C$6)</f>
-        <v>179.672454545455</v>
+        <v>178.707909090909</v>
       </c>
       <c r="E22" s="16">
         <f>D22*Assumptions!$C$8</f>
-        <v>4851.15627272727</v>
+        <v>4825.11354545455</v>
       </c>
       <c r="F22" s="18">
         <f>IFERROR(E22/C22,0)</f>
@@ -1671,24 +1671,24 @@
       </c>
       <c r="G22" s="17">
         <f>D22/40</f>
-        <v>4.49181136363636</v>
+        <v>4.46769772727273</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="15" t="n">
-        <v>46305</v>
+        <v>46314</v>
       </c>
       <c r="C23" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B23)</f>
-        <v>19587.54</v>
+        <v>20336.76</v>
       </c>
       <c r="D23" s="17">
         <f>MAX(Assumptions!$C$7*7,C23/Assumptions!$C$6)</f>
-        <v>178.068545454545</v>
+        <v>184.879636363636</v>
       </c>
       <c r="E23" s="16">
         <f>D23*Assumptions!$C$8</f>
-        <v>4807.85072727273</v>
+        <v>4991.75018181818</v>
       </c>
       <c r="F23" s="18">
         <f>IFERROR(E23/C23,0)</f>
@@ -1696,24 +1696,24 @@
       </c>
       <c r="G23" s="17">
         <f>D23/40</f>
-        <v>4.45171363636364</v>
+        <v>4.62199090909091</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="15" t="n">
-        <v>46312</v>
+        <v>46321</v>
       </c>
       <c r="C24" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B24)</f>
-        <v>19999.31</v>
+        <v>19047.27</v>
       </c>
       <c r="D24" s="17">
         <f>MAX(Assumptions!$C$7*7,C24/Assumptions!$C$6)</f>
-        <v>181.811909090909</v>
+        <v>173.157</v>
       </c>
       <c r="E24" s="16">
         <f>D24*Assumptions!$C$8</f>
-        <v>4908.92154545455</v>
+        <v>4675.239</v>
       </c>
       <c r="F24" s="18">
         <f>IFERROR(E24/C24,0)</f>
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G24" s="17">
         <f>D24/40</f>
-        <v>4.54529772727273</v>
+        <v>4.328925</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="15" t="n">
-        <v>46319</v>
+        <v>46328</v>
       </c>
       <c r="C25" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B25)</f>
-        <v>20093.27</v>
+        <v>21468.36</v>
       </c>
       <c r="D25" s="17">
         <f>MAX(Assumptions!$C$7*7,C25/Assumptions!$C$6)</f>
-        <v>182.666090909091</v>
+        <v>195.166909090909</v>
       </c>
       <c r="E25" s="16">
         <f>D25*Assumptions!$C$8</f>
-        <v>4931.98445454545</v>
+        <v>5269.50654545455</v>
       </c>
       <c r="F25" s="18">
         <f>IFERROR(E25/C25,0)</f>
@@ -1746,24 +1746,24 @@
       </c>
       <c r="G25" s="17">
         <f>D25/40</f>
-        <v>4.56665227272727</v>
+        <v>4.87917272727273</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="15" t="n">
-        <v>46326</v>
+        <v>46335</v>
       </c>
       <c r="C26" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B26)</f>
-        <v>20478.63</v>
+        <v>21326.85</v>
       </c>
       <c r="D26" s="17">
         <f>MAX(Assumptions!$C$7*7,C26/Assumptions!$C$6)</f>
-        <v>186.169363636364</v>
+        <v>193.880454545455</v>
       </c>
       <c r="E26" s="16">
         <f>D26*Assumptions!$C$8</f>
-        <v>5026.57281818182</v>
+        <v>5234.77227272727</v>
       </c>
       <c r="F26" s="18">
         <f>IFERROR(E26/C26,0)</f>
@@ -1771,24 +1771,24 @@
       </c>
       <c r="G26" s="17">
         <f>D26/40</f>
-        <v>4.65423409090909</v>
+        <v>4.84701136363636</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="15" t="n">
-        <v>46333</v>
+        <v>46342</v>
       </c>
       <c r="C27" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B27)</f>
-        <v>21381.07</v>
+        <v>21203.71</v>
       </c>
       <c r="D27" s="17">
         <f>MAX(Assumptions!$C$7*7,C27/Assumptions!$C$6)</f>
-        <v>194.373363636364</v>
+        <v>192.761</v>
       </c>
       <c r="E27" s="16">
         <f>D27*Assumptions!$C$8</f>
-        <v>5248.08081818182</v>
+        <v>5204.547</v>
       </c>
       <c r="F27" s="18">
         <f>IFERROR(E27/C27,0)</f>
@@ -1796,24 +1796,24 @@
       </c>
       <c r="G27" s="17">
         <f>D27/40</f>
-        <v>4.85933409090909</v>
+        <v>4.819025</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="15" t="n">
-        <v>46340</v>
+        <v>46349</v>
       </c>
       <c r="C28" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B28)</f>
-        <v>21226.65</v>
+        <v>21889.32</v>
       </c>
       <c r="D28" s="17">
         <f>MAX(Assumptions!$C$7*7,C28/Assumptions!$C$6)</f>
-        <v>192.969545454545</v>
+        <v>198.993818181818</v>
       </c>
       <c r="E28" s="16">
         <f>D28*Assumptions!$C$8</f>
-        <v>5210.17772727273</v>
+        <v>5372.83309090909</v>
       </c>
       <c r="F28" s="18">
         <f>IFERROR(E28/C28,0)</f>
@@ -1821,24 +1821,24 @@
       </c>
       <c r="G28" s="17">
         <f>D28/40</f>
-        <v>4.82423863636364</v>
+        <v>4.97484545454545</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="15" t="n">
-        <v>46347</v>
+        <v>46356</v>
       </c>
       <c r="C29" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B29)</f>
-        <v>21515.39</v>
+        <v>23828.14</v>
       </c>
       <c r="D29" s="17">
         <f>MAX(Assumptions!$C$7*7,C29/Assumptions!$C$6)</f>
-        <v>195.594454545455</v>
+        <v>216.619454545455</v>
       </c>
       <c r="E29" s="16">
         <f>D29*Assumptions!$C$8</f>
-        <v>5281.05027272727</v>
+        <v>5848.72527272727</v>
       </c>
       <c r="F29" s="18">
         <f>IFERROR(E29/C29,0)</f>
@@ -1846,24 +1846,24 @@
       </c>
       <c r="G29" s="17">
         <f>D29/40</f>
-        <v>4.88986136363636</v>
+        <v>5.41548636363636</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="15" t="n">
-        <v>46354</v>
+        <v>46363</v>
       </c>
       <c r="C30" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B30)</f>
-        <v>22912.01</v>
+        <v>23146.13</v>
       </c>
       <c r="D30" s="17">
         <f>MAX(Assumptions!$C$7*7,C30/Assumptions!$C$6)</f>
-        <v>208.291</v>
+        <v>210.419363636364</v>
       </c>
       <c r="E30" s="16">
         <f>D30*Assumptions!$C$8</f>
-        <v>5623.857</v>
+        <v>5681.32281818182</v>
       </c>
       <c r="F30" s="18">
         <f>IFERROR(E30/C30,0)</f>
@@ -1871,24 +1871,24 @@
       </c>
       <c r="G30" s="17">
         <f>D30/40</f>
-        <v>5.207275</v>
+        <v>5.26048409090909</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="15" t="n">
-        <v>46361</v>
+        <v>46370</v>
       </c>
       <c r="C31" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B31)</f>
-        <v>23487.6</v>
+        <v>23704.91</v>
       </c>
       <c r="D31" s="17">
         <f>MAX(Assumptions!$C$7*7,C31/Assumptions!$C$6)</f>
-        <v>213.523636363636</v>
+        <v>215.499181818182</v>
       </c>
       <c r="E31" s="16">
         <f>D31*Assumptions!$C$8</f>
-        <v>5765.13818181818</v>
+        <v>5818.47790909091</v>
       </c>
       <c r="F31" s="18">
         <f>IFERROR(E31/C31,0)</f>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G31" s="17">
         <f>D31/40</f>
-        <v>5.33809090909091</v>
+        <v>5.38747954545455</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="15" t="n">
-        <v>46368</v>
+        <v>46377</v>
       </c>
       <c r="C32" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B32)</f>
-        <v>24015.31</v>
+        <v>21888.02</v>
       </c>
       <c r="D32" s="17">
         <f>MAX(Assumptions!$C$7*7,C32/Assumptions!$C$6)</f>
-        <v>218.321</v>
+        <v>198.982</v>
       </c>
       <c r="E32" s="16">
         <f>D32*Assumptions!$C$8</f>
-        <v>5894.667</v>
+        <v>5372.514</v>
       </c>
       <c r="F32" s="18">
         <f>IFERROR(E32/C32,0)</f>
@@ -1921,24 +1921,24 @@
       </c>
       <c r="G32" s="17">
         <f>D32/40</f>
-        <v>5.458025</v>
+        <v>4.97455</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="15" t="n">
-        <v>46375</v>
+        <v>46384</v>
       </c>
       <c r="C33" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B33)</f>
-        <v>22249.98</v>
+        <v>19071.55</v>
       </c>
       <c r="D33" s="17">
         <f>MAX(Assumptions!$C$7*7,C33/Assumptions!$C$6)</f>
-        <v>202.272545454545</v>
+        <v>173.377727272727</v>
       </c>
       <c r="E33" s="16">
         <f>D33*Assumptions!$C$8</f>
-        <v>5461.35872727273</v>
+        <v>4681.19863636364</v>
       </c>
       <c r="F33" s="18">
         <f>IFERROR(E33/C33,0)</f>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G33" s="17">
         <f>D33/40</f>
-        <v>5.05681363636364</v>
+        <v>4.33444318181818</v>
       </c>
     </row>
     <row r="34">
@@ -1957,15 +1957,15 @@
       </c>
       <c r="C34" s="21">
         <f>SUM(C21:C33)</f>
-        <v>275812.16</v>
+        <v>275917.43</v>
       </c>
       <c r="D34" s="22">
         <f>SUM(D21:D33)</f>
-        <v>2507.38327272727</v>
+        <v>2508.34027272727</v>
       </c>
       <c r="E34" s="21">
         <f>SUM(E21:E33)</f>
-        <v>67699.3483636364</v>
+        <v>67725.1873636364</v>
       </c>
       <c r="F34" s="23">
         <f>IFERROR(E34/C34,0)</f>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="G34" s="22">
         <f>IFERROR(AVERAGE(G21:G33),0)</f>
-        <v>4.82189090909091</v>
+        <v>4.82373129370629</v>
       </c>
     </row>
   </sheetData>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B7" s="25" t="n">
-        <v>19101.42</v>
+        <v>19348.54</v>
       </c>
     </row>
     <row r="8">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="B8" s="25" t="n">
-        <v>275812.16</v>
+        <v>275917.43</v>
       </c>
     </row>
     <row r="9">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>294913.58</v>
+        <v>295265.97</v>
       </c>
     </row>
   </sheetData>
@@ -2155,7 +2155,7 @@
     </row>
     <row r="2">
       <c r="A2" s="27" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="B2" s="28" t="inlineStr">
         <is>
@@ -2163,12 +2163,12 @@
         </is>
       </c>
       <c r="C2" s="29" t="n">
-        <v>2373.37</v>
+        <v>2953.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="27" t="n">
-        <v>46292</v>
+        <v>46301</v>
       </c>
       <c r="B3" s="28" t="inlineStr">
         <is>
@@ -2176,12 +2176,12 @@
         </is>
       </c>
       <c r="C3" s="29" t="n">
-        <v>1985.41</v>
+        <v>2940.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="27" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
@@ -2189,12 +2189,12 @@
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>2827.57</v>
+        <v>2986.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="27" t="n">
-        <v>46294</v>
+        <v>46303</v>
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
@@ -2202,12 +2202,12 @@
         </is>
       </c>
       <c r="C5" s="29" t="n">
-        <v>2925.14</v>
+        <v>2963.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="27" t="n">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
@@ -2215,12 +2215,12 @@
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>2949.26</v>
+        <v>3040.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="n">
-        <v>46296</v>
+        <v>46305</v>
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
@@ -2228,12 +2228,12 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>3000.51</v>
+        <v>2360.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="27" t="n">
-        <v>46297</v>
+        <v>46306</v>
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
@@ -2241,12 +2241,12 @@
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>3040.16</v>
+        <v>2102.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="n">
-        <v>46291</v>
+        <v>46300</v>
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
@@ -2254,12 +2254,12 @@
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>19101.43</v>
+        <v>19348.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="27" t="n">
-        <v>46298</v>
+        <v>46307</v>
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
@@ -2267,12 +2267,12 @@
         </is>
       </c>
       <c r="C10" s="29" t="n">
-        <v>19763.97</v>
+        <v>19657.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="27" t="n">
-        <v>46305</v>
+        <v>46314</v>
       </c>
       <c r="B11" s="28" t="inlineStr">
         <is>
@@ -2280,12 +2280,12 @@
         </is>
       </c>
       <c r="C11" s="29" t="n">
-        <v>19587.54</v>
+        <v>20336.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="n">
-        <v>46312</v>
+        <v>46321</v>
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
@@ -2293,12 +2293,12 @@
         </is>
       </c>
       <c r="C12" s="29" t="n">
-        <v>19999.31</v>
+        <v>19047.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="27" t="n">
-        <v>46319</v>
+        <v>46328</v>
       </c>
       <c r="B13" s="28" t="inlineStr">
         <is>
@@ -2306,12 +2306,12 @@
         </is>
       </c>
       <c r="C13" s="29" t="n">
-        <v>20093.27</v>
+        <v>21468.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="27" t="n">
-        <v>46326</v>
+        <v>46335</v>
       </c>
       <c r="B14" s="28" t="inlineStr">
         <is>
@@ -2319,12 +2319,12 @@
         </is>
       </c>
       <c r="C14" s="29" t="n">
-        <v>20478.63</v>
+        <v>21326.85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="27" t="n">
-        <v>46333</v>
+        <v>46342</v>
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
@@ -2332,12 +2332,12 @@
         </is>
       </c>
       <c r="C15" s="29" t="n">
-        <v>21381.07</v>
+        <v>21203.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="27" t="n">
-        <v>46340</v>
+        <v>46349</v>
       </c>
       <c r="B16" s="28" t="inlineStr">
         <is>
@@ -2345,12 +2345,12 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>21226.65</v>
+        <v>21889.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="27" t="n">
-        <v>46347</v>
+        <v>46356</v>
       </c>
       <c r="B17" s="28" t="inlineStr">
         <is>
@@ -2358,12 +2358,12 @@
         </is>
       </c>
       <c r="C17" s="29" t="n">
-        <v>21515.39</v>
+        <v>23828.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="27" t="n">
-        <v>46354</v>
+        <v>46363</v>
       </c>
       <c r="B18" s="28" t="inlineStr">
         <is>
@@ -2371,12 +2371,12 @@
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>22912.01</v>
+        <v>23146.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="27" t="n">
-        <v>46361</v>
+        <v>46370</v>
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
@@ -2384,12 +2384,12 @@
         </is>
       </c>
       <c r="C19" s="29" t="n">
-        <v>23487.6</v>
+        <v>23704.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="27" t="n">
-        <v>46368</v>
+        <v>46377</v>
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
@@ -2397,12 +2397,12 @@
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>24015.31</v>
+        <v>21888.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="27" t="n">
-        <v>46375</v>
+        <v>46384</v>
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="C21" s="29" t="n">
-        <v>22249.98</v>
+        <v>19071.55</v>
       </c>
     </row>
   </sheetData>
@@ -2667,7 +2667,7 @@
     <row r="6">
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.4.0.</t>
+          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 04 Oct 2026.  Shelly v1.6.0.</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 03 Oct 2026 05:51</t>
+          <t>Generated by Shelly on 04 Oct 2026 20:46</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Roster_Labour.xlsx
+++ b/docs/reports/Shelly_Roster_Labour.xlsx
@@ -562,14 +562,13 @@
   <cacheFields count="3">
     <cacheField name="Date" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
       <sharedItems count="19">
-        <s v="2026-10-05"/>
-        <s v="2026-10-06"/>
-        <s v="2026-10-07"/>
-        <s v="2026-10-08"/>
-        <s v="2026-10-09"/>
-        <s v="2026-10-10"/>
-        <s v="2026-10-11"/>
         <s v="2026-10-12"/>
+        <s v="2026-10-13"/>
+        <s v="2026-10-14"/>
+        <s v="2026-10-15"/>
+        <s v="2026-10-16"/>
+        <s v="2026-10-17"/>
+        <s v="2026-10-18"/>
         <s v="2026-10-19"/>
         <s v="2026-10-26"/>
         <s v="2026-11-02"/>
@@ -581,6 +580,7 @@
         <s v="2026-12-14"/>
         <s v="2026-12-21"/>
         <s v="2026-12-28"/>
+        <s v="2027-01-04"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Type" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
@@ -590,7 +590,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Forecast sales" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="2102.99" maxValue="23828.14"/>
+      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="2102.42" maxValue="23790.29"/>
     </cacheField>
   </cacheFields>
 </pivotCacheDefinition>
@@ -601,102 +601,102 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="2953.86"/>
+    <n v="3050.03"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
-    <n v="2940.45"/>
+    <n v="3029.57"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
-    <n v="2986.75"/>
+    <n v="2955.89"/>
   </r>
   <r>
     <x v="3"/>
     <x v="0"/>
-    <n v="2963.84"/>
+    <n v="3203.6"/>
   </r>
   <r>
     <x v="4"/>
     <x v="0"/>
-    <n v="3040.24"/>
+    <n v="3247.61"/>
   </r>
   <r>
     <x v="5"/>
     <x v="0"/>
-    <n v="2360.41"/>
+    <n v="2502.67"/>
   </r>
   <r>
     <x v="6"/>
     <x v="0"/>
-    <n v="2102.99"/>
+    <n v="2102.42"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="19348.54"/>
+    <n v="20091.79"/>
   </r>
   <r>
     <x v="7"/>
     <x v="1"/>
-    <n v="19657.87"/>
+    <n v="20879.38"/>
   </r>
   <r>
     <x v="8"/>
     <x v="1"/>
-    <n v="20336.76"/>
+    <n v="19819.66"/>
   </r>
   <r>
     <x v="9"/>
     <x v="1"/>
-    <n v="19047.27"/>
+    <n v="21739.04"/>
   </r>
   <r>
     <x v="10"/>
     <x v="1"/>
-    <n v="21468.36"/>
+    <n v="20952.55"/>
   </r>
   <r>
     <x v="11"/>
     <x v="1"/>
-    <n v="21326.85"/>
+    <n v="21464.6"/>
   </r>
   <r>
     <x v="12"/>
     <x v="1"/>
-    <n v="21203.71"/>
+    <n v="20629.81"/>
   </r>
   <r>
     <x v="13"/>
     <x v="1"/>
-    <n v="21889.32"/>
+    <n v="23790.29"/>
   </r>
   <r>
     <x v="14"/>
     <x v="1"/>
-    <n v="23828.14"/>
+    <n v="23214.98"/>
   </r>
   <r>
     <x v="15"/>
     <x v="1"/>
-    <n v="23146.13"/>
+    <n v="23268.04"/>
   </r>
   <r>
     <x v="16"/>
     <x v="1"/>
-    <n v="23704.91"/>
+    <n v="20933.69"/>
   </r>
   <r>
     <x v="17"/>
     <x v="1"/>
-    <n v="21888.02"/>
+    <n v="20028.24"/>
   </r>
   <r>
     <x v="18"/>
     <x v="1"/>
-    <n v="19071.55"/>
+    <n v="18936.58"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -1104,7 +1104,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Demo Neighbourhood Store (Eden Terrace format) · from 05 Oct 2026</t>
+          <t>Demo Neighbourhood Store (Eden Terrace format) · from 12 Oct 2026</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1170,22 +1170,22 @@
     <row r="10">
       <c r="B10" s="10">
         <f>Model!$D$15</f>
-        <v>183.319454545455</v>
+        <v>188.788181818182</v>
       </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="11">
         <f>Model!$E$15</f>
-        <v>4949.62527272727</v>
+        <v>5097.28090909091</v>
       </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="12">
         <f>Model!$F$15</f>
-        <v>0.255813889457668</v>
+        <v>0.253699690723968</v>
       </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="11">
         <f>Model!$E$34</f>
-        <v>67725.1873636364</v>
+        <v>67683.7595454546</v>
       </c>
       <c r="M10" s="9" t="n"/>
     </row>
@@ -1216,12 +1216,12 @@
     <row r="14">
       <c r="B14" s="10">
         <f>Model!$D$34</f>
-        <v>2508.34027272727</v>
+        <v>2506.80590909091</v>
       </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="10">
         <f>Model!$G$34</f>
-        <v>4.82373129370629</v>
+        <v>4.82078059440559</v>
       </c>
       <c r="G14" s="9" t="n"/>
     </row>
@@ -1385,19 +1385,19 @@
     </row>
     <row r="8">
       <c r="B8" s="15" t="n">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="C8" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B8)</f>
-        <v>2953.86</v>
+        <v>3050.03</v>
       </c>
       <c r="D8" s="17">
         <f>MAX(Assumptions!$C$7,C8/Assumptions!$C$6)</f>
-        <v>26.8532727272727</v>
+        <v>27.7275454545455</v>
       </c>
       <c r="E8" s="16">
         <f>D8*Assumptions!$C$8</f>
-        <v>725.038363636364</v>
+        <v>748.643727272727</v>
       </c>
       <c r="F8" s="18">
         <f>IFERROR(E8/C8,0)</f>
@@ -1410,19 +1410,19 @@
     </row>
     <row r="9">
       <c r="B9" s="15" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="C9" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B9)</f>
-        <v>2940.45</v>
+        <v>3029.57</v>
       </c>
       <c r="D9" s="17">
         <f>MAX(Assumptions!$C$7,C9/Assumptions!$C$6)</f>
-        <v>26.7313636363636</v>
+        <v>27.5415454545455</v>
       </c>
       <c r="E9" s="16">
         <f>D9*Assumptions!$C$8</f>
-        <v>721.746818181818</v>
+        <v>743.621727272727</v>
       </c>
       <c r="F9" s="18">
         <f>IFERROR(E9/C9,0)</f>
@@ -1435,19 +1435,19 @@
     </row>
     <row r="10">
       <c r="B10" s="15" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="C10" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B10)</f>
-        <v>2986.75</v>
+        <v>2955.89</v>
       </c>
       <c r="D10" s="17">
         <f>MAX(Assumptions!$C$7,C10/Assumptions!$C$6)</f>
-        <v>27.1522727272727</v>
+        <v>26.8717272727273</v>
       </c>
       <c r="E10" s="16">
         <f>D10*Assumptions!$C$8</f>
-        <v>733.111363636364</v>
+        <v>725.536636363636</v>
       </c>
       <c r="F10" s="18">
         <f>IFERROR(E10/C10,0)</f>
@@ -1460,19 +1460,19 @@
     </row>
     <row r="11">
       <c r="B11" s="15" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="C11" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B11)</f>
-        <v>2963.84</v>
+        <v>3203.6</v>
       </c>
       <c r="D11" s="17">
         <f>MAX(Assumptions!$C$7,C11/Assumptions!$C$6)</f>
-        <v>26.944</v>
+        <v>29.1236363636364</v>
       </c>
       <c r="E11" s="16">
         <f>D11*Assumptions!$C$8</f>
-        <v>727.488</v>
+        <v>786.338181818182</v>
       </c>
       <c r="F11" s="18">
         <f>IFERROR(E11/C11,0)</f>
@@ -1485,19 +1485,19 @@
     </row>
     <row r="12">
       <c r="B12" s="15" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B12)</f>
-        <v>3040.24</v>
+        <v>3247.61</v>
       </c>
       <c r="D12" s="17">
         <f>MAX(Assumptions!$C$7,C12/Assumptions!$C$6)</f>
-        <v>27.6385454545455</v>
+        <v>29.5237272727273</v>
       </c>
       <c r="E12" s="16">
         <f>D12*Assumptions!$C$8</f>
-        <v>746.240727272727</v>
+        <v>797.140636363636</v>
       </c>
       <c r="F12" s="18">
         <f>IFERROR(E12/C12,0)</f>
@@ -1510,11 +1510,11 @@
     </row>
     <row r="13">
       <c r="B13" s="15" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="C13" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B13)</f>
-        <v>2360.41</v>
+        <v>2502.67</v>
       </c>
       <c r="D13" s="17">
         <f>MAX(Assumptions!$C$7,C13/Assumptions!$C$6)</f>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F13" s="18">
         <f>IFERROR(E13/C13,0)</f>
-        <v>0.274528577662355</v>
+        <v>0.258923469734324</v>
       </c>
       <c r="G13" s="19">
         <f>ROUNDUP(D13/8,0)</f>
@@ -1535,11 +1535,11 @@
     </row>
     <row r="14">
       <c r="B14" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="C14" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Day",Raw!$A$2:$A$21,$B14)</f>
-        <v>2102.99</v>
+        <v>2102.42</v>
       </c>
       <c r="D14" s="17">
         <f>MAX(Assumptions!$C$7,C14/Assumptions!$C$6)</f>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F14" s="18">
         <f>IFERROR(E14/C14,0)</f>
-        <v>0.308132706289616</v>
+        <v>0.308216246040277</v>
       </c>
       <c r="G14" s="19">
         <f>ROUNDUP(D14/8,0)</f>
@@ -1566,19 +1566,19 @@
       </c>
       <c r="C15" s="21">
         <f>SUM(C8:C14)</f>
-        <v>19348.54</v>
+        <v>20091.79</v>
       </c>
       <c r="D15" s="22">
         <f>SUM(D8:D14)</f>
-        <v>183.319454545455</v>
+        <v>188.788181818182</v>
       </c>
       <c r="E15" s="21">
         <f>SUM(E8:E14)</f>
-        <v>4949.62527272727</v>
+        <v>5097.28090909091</v>
       </c>
       <c r="F15" s="23">
         <f>IFERROR(E15/C15,0)</f>
-        <v>0.255813889457668</v>
+        <v>0.253699690723968</v>
       </c>
       <c r="G15" s="24">
         <f>SUM(G8:G14)</f>
@@ -1626,19 +1626,19 @@
     </row>
     <row r="21">
       <c r="B21" s="15" t="n">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="C21" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B21)</f>
-        <v>19348.54</v>
+        <v>20091.79</v>
       </c>
       <c r="D21" s="17">
         <f>MAX(Assumptions!$C$7*7,C21/Assumptions!$C$6)</f>
-        <v>175.895818181818</v>
+        <v>182.652636363636</v>
       </c>
       <c r="E21" s="16">
         <f>D21*Assumptions!$C$8</f>
-        <v>4749.18709090909</v>
+        <v>4931.62118181818</v>
       </c>
       <c r="F21" s="18">
         <f>IFERROR(E21/C21,0)</f>
@@ -1646,24 +1646,24 @@
       </c>
       <c r="G21" s="17">
         <f>D21/40</f>
-        <v>4.39739545454546</v>
+        <v>4.56631590909091</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="15" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="C22" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B22)</f>
-        <v>19657.87</v>
+        <v>20879.38</v>
       </c>
       <c r="D22" s="17">
         <f>MAX(Assumptions!$C$7*7,C22/Assumptions!$C$6)</f>
-        <v>178.707909090909</v>
+        <v>189.812545454545</v>
       </c>
       <c r="E22" s="16">
         <f>D22*Assumptions!$C$8</f>
-        <v>4825.11354545455</v>
+        <v>5124.93872727273</v>
       </c>
       <c r="F22" s="18">
         <f>IFERROR(E22/C22,0)</f>
@@ -1671,24 +1671,24 @@
       </c>
       <c r="G22" s="17">
         <f>D22/40</f>
-        <v>4.46769772727273</v>
+        <v>4.74531363636364</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="15" t="n">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="C23" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B23)</f>
-        <v>20336.76</v>
+        <v>19819.66</v>
       </c>
       <c r="D23" s="17">
         <f>MAX(Assumptions!$C$7*7,C23/Assumptions!$C$6)</f>
-        <v>184.879636363636</v>
+        <v>180.178727272727</v>
       </c>
       <c r="E23" s="16">
         <f>D23*Assumptions!$C$8</f>
-        <v>4991.75018181818</v>
+        <v>4864.82563636364</v>
       </c>
       <c r="F23" s="18">
         <f>IFERROR(E23/C23,0)</f>
@@ -1696,24 +1696,24 @@
       </c>
       <c r="G23" s="17">
         <f>D23/40</f>
-        <v>4.62199090909091</v>
+        <v>4.50446818181818</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="15" t="n">
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="C24" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B24)</f>
-        <v>19047.27</v>
+        <v>21739.04</v>
       </c>
       <c r="D24" s="17">
         <f>MAX(Assumptions!$C$7*7,C24/Assumptions!$C$6)</f>
-        <v>173.157</v>
+        <v>197.627636363636</v>
       </c>
       <c r="E24" s="16">
         <f>D24*Assumptions!$C$8</f>
-        <v>4675.239</v>
+        <v>5335.94618181818</v>
       </c>
       <c r="F24" s="18">
         <f>IFERROR(E24/C24,0)</f>
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G24" s="17">
         <f>D24/40</f>
-        <v>4.328925</v>
+        <v>4.94069090909091</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="15" t="n">
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="C25" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B25)</f>
-        <v>21468.36</v>
+        <v>20952.55</v>
       </c>
       <c r="D25" s="17">
         <f>MAX(Assumptions!$C$7*7,C25/Assumptions!$C$6)</f>
-        <v>195.166909090909</v>
+        <v>190.477727272727</v>
       </c>
       <c r="E25" s="16">
         <f>D25*Assumptions!$C$8</f>
-        <v>5269.50654545455</v>
+        <v>5142.89863636364</v>
       </c>
       <c r="F25" s="18">
         <f>IFERROR(E25/C25,0)</f>
@@ -1746,24 +1746,24 @@
       </c>
       <c r="G25" s="17">
         <f>D25/40</f>
-        <v>4.87917272727273</v>
+        <v>4.76194318181818</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="15" t="n">
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="C26" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B26)</f>
-        <v>21326.85</v>
+        <v>21464.6</v>
       </c>
       <c r="D26" s="17">
         <f>MAX(Assumptions!$C$7*7,C26/Assumptions!$C$6)</f>
-        <v>193.880454545455</v>
+        <v>195.132727272727</v>
       </c>
       <c r="E26" s="16">
         <f>D26*Assumptions!$C$8</f>
-        <v>5234.77227272727</v>
+        <v>5268.58363636364</v>
       </c>
       <c r="F26" s="18">
         <f>IFERROR(E26/C26,0)</f>
@@ -1771,24 +1771,24 @@
       </c>
       <c r="G26" s="17">
         <f>D26/40</f>
-        <v>4.84701136363636</v>
+        <v>4.87831818181818</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="15" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="C27" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B27)</f>
-        <v>21203.71</v>
+        <v>20629.81</v>
       </c>
       <c r="D27" s="17">
         <f>MAX(Assumptions!$C$7*7,C27/Assumptions!$C$6)</f>
-        <v>192.761</v>
+        <v>187.543727272727</v>
       </c>
       <c r="E27" s="16">
         <f>D27*Assumptions!$C$8</f>
-        <v>5204.547</v>
+        <v>5063.68063636364</v>
       </c>
       <c r="F27" s="18">
         <f>IFERROR(E27/C27,0)</f>
@@ -1796,24 +1796,24 @@
       </c>
       <c r="G27" s="17">
         <f>D27/40</f>
-        <v>4.819025</v>
+        <v>4.68859318181818</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="15" t="n">
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="C28" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B28)</f>
-        <v>21889.32</v>
+        <v>23790.29</v>
       </c>
       <c r="D28" s="17">
         <f>MAX(Assumptions!$C$7*7,C28/Assumptions!$C$6)</f>
-        <v>198.993818181818</v>
+        <v>216.275363636364</v>
       </c>
       <c r="E28" s="16">
         <f>D28*Assumptions!$C$8</f>
-        <v>5372.83309090909</v>
+        <v>5839.43481818182</v>
       </c>
       <c r="F28" s="18">
         <f>IFERROR(E28/C28,0)</f>
@@ -1821,24 +1821,24 @@
       </c>
       <c r="G28" s="17">
         <f>D28/40</f>
-        <v>4.97484545454545</v>
+        <v>5.40688409090909</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="15" t="n">
-        <v>46356</v>
+        <v>46363</v>
       </c>
       <c r="C29" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B29)</f>
-        <v>23828.14</v>
+        <v>23214.98</v>
       </c>
       <c r="D29" s="17">
         <f>MAX(Assumptions!$C$7*7,C29/Assumptions!$C$6)</f>
-        <v>216.619454545455</v>
+        <v>211.045272727273</v>
       </c>
       <c r="E29" s="16">
         <f>D29*Assumptions!$C$8</f>
-        <v>5848.72527272727</v>
+        <v>5698.22236363636</v>
       </c>
       <c r="F29" s="18">
         <f>IFERROR(E29/C29,0)</f>
@@ -1846,24 +1846,24 @@
       </c>
       <c r="G29" s="17">
         <f>D29/40</f>
-        <v>5.41548636363636</v>
+        <v>5.27613181818182</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="15" t="n">
-        <v>46363</v>
+        <v>46370</v>
       </c>
       <c r="C30" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B30)</f>
-        <v>23146.13</v>
+        <v>23268.04</v>
       </c>
       <c r="D30" s="17">
         <f>MAX(Assumptions!$C$7*7,C30/Assumptions!$C$6)</f>
-        <v>210.419363636364</v>
+        <v>211.527636363636</v>
       </c>
       <c r="E30" s="16">
         <f>D30*Assumptions!$C$8</f>
-        <v>5681.32281818182</v>
+        <v>5711.24618181818</v>
       </c>
       <c r="F30" s="18">
         <f>IFERROR(E30/C30,0)</f>
@@ -1871,24 +1871,24 @@
       </c>
       <c r="G30" s="17">
         <f>D30/40</f>
-        <v>5.26048409090909</v>
+        <v>5.28819090909091</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="15" t="n">
-        <v>46370</v>
+        <v>46377</v>
       </c>
       <c r="C31" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B31)</f>
-        <v>23704.91</v>
+        <v>20933.69</v>
       </c>
       <c r="D31" s="17">
         <f>MAX(Assumptions!$C$7*7,C31/Assumptions!$C$6)</f>
-        <v>215.499181818182</v>
+        <v>190.306272727273</v>
       </c>
       <c r="E31" s="16">
         <f>D31*Assumptions!$C$8</f>
-        <v>5818.47790909091</v>
+        <v>5138.26936363636</v>
       </c>
       <c r="F31" s="18">
         <f>IFERROR(E31/C31,0)</f>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G31" s="17">
         <f>D31/40</f>
-        <v>5.38747954545455</v>
+        <v>4.75765681818182</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="15" t="n">
-        <v>46377</v>
+        <v>46384</v>
       </c>
       <c r="C32" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B32)</f>
-        <v>21888.02</v>
+        <v>20028.24</v>
       </c>
       <c r="D32" s="17">
         <f>MAX(Assumptions!$C$7*7,C32/Assumptions!$C$6)</f>
-        <v>198.982</v>
+        <v>182.074909090909</v>
       </c>
       <c r="E32" s="16">
         <f>D32*Assumptions!$C$8</f>
-        <v>5372.514</v>
+        <v>4916.02254545455</v>
       </c>
       <c r="F32" s="18">
         <f>IFERROR(E32/C32,0)</f>
@@ -1921,24 +1921,24 @@
       </c>
       <c r="G32" s="17">
         <f>D32/40</f>
-        <v>4.97455</v>
+        <v>4.55187272727273</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="15" t="n">
-        <v>46384</v>
+        <v>46391</v>
       </c>
       <c r="C33" s="16">
         <f>SUMIFS(Raw!$C$2:$C$21,Raw!$B$2:$B$21,"Week",Raw!$A$2:$A$21,$B33)</f>
-        <v>19071.55</v>
+        <v>18936.58</v>
       </c>
       <c r="D33" s="17">
         <f>MAX(Assumptions!$C$7*7,C33/Assumptions!$C$6)</f>
-        <v>173.377727272727</v>
+        <v>172.150727272727</v>
       </c>
       <c r="E33" s="16">
         <f>D33*Assumptions!$C$8</f>
-        <v>4681.19863636364</v>
+        <v>4648.06963636364</v>
       </c>
       <c r="F33" s="18">
         <f>IFERROR(E33/C33,0)</f>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G33" s="17">
         <f>D33/40</f>
-        <v>4.33444318181818</v>
+        <v>4.30376818181818</v>
       </c>
     </row>
     <row r="34">
@@ -1957,15 +1957,15 @@
       </c>
       <c r="C34" s="21">
         <f>SUM(C21:C33)</f>
-        <v>275917.43</v>
+        <v>275748.65</v>
       </c>
       <c r="D34" s="22">
         <f>SUM(D21:D33)</f>
-        <v>2508.34027272727</v>
+        <v>2506.80590909091</v>
       </c>
       <c r="E34" s="21">
         <f>SUM(E21:E33)</f>
-        <v>67725.1873636364</v>
+        <v>67683.7595454546</v>
       </c>
       <c r="F34" s="23">
         <f>IFERROR(E34/C34,0)</f>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="G34" s="22">
         <f>IFERROR(AVERAGE(G21:G33),0)</f>
-        <v>4.82373129370629</v>
+        <v>4.82078059440559</v>
       </c>
     </row>
   </sheetData>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B7" s="25" t="n">
-        <v>19348.54</v>
+        <v>20091.79</v>
       </c>
     </row>
     <row r="8">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="B8" s="25" t="n">
-        <v>275917.43</v>
+        <v>275748.65</v>
       </c>
     </row>
     <row r="9">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>295265.97</v>
+        <v>295840.44</v>
       </c>
     </row>
   </sheetData>
@@ -2155,7 +2155,7 @@
     </row>
     <row r="2">
       <c r="A2" s="27" t="n">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="B2" s="28" t="inlineStr">
         <is>
@@ -2163,12 +2163,12 @@
         </is>
       </c>
       <c r="C2" s="29" t="n">
-        <v>2953.86</v>
+        <v>3050.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="27" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="B3" s="28" t="inlineStr">
         <is>
@@ -2176,12 +2176,12 @@
         </is>
       </c>
       <c r="C3" s="29" t="n">
-        <v>2940.45</v>
+        <v>3029.57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="27" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
@@ -2189,12 +2189,12 @@
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>2986.75</v>
+        <v>2955.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="27" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
@@ -2202,12 +2202,12 @@
         </is>
       </c>
       <c r="C5" s="29" t="n">
-        <v>2963.84</v>
+        <v>3203.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="27" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
@@ -2215,12 +2215,12 @@
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>3040.24</v>
+        <v>3247.61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
@@ -2228,12 +2228,12 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>2360.41</v>
+        <v>2502.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="27" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
@@ -2241,12 +2241,12 @@
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>2102.99</v>
+        <v>2102.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="n">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
@@ -2254,12 +2254,12 @@
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>19348.54</v>
+        <v>20091.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="27" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
@@ -2267,12 +2267,12 @@
         </is>
       </c>
       <c r="C10" s="29" t="n">
-        <v>19657.87</v>
+        <v>20879.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="27" t="n">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="B11" s="28" t="inlineStr">
         <is>
@@ -2280,12 +2280,12 @@
         </is>
       </c>
       <c r="C11" s="29" t="n">
-        <v>20336.76</v>
+        <v>19819.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="n">
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
@@ -2293,12 +2293,12 @@
         </is>
       </c>
       <c r="C12" s="29" t="n">
-        <v>19047.27</v>
+        <v>21739.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="27" t="n">
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="B13" s="28" t="inlineStr">
         <is>
@@ -2306,12 +2306,12 @@
         </is>
       </c>
       <c r="C13" s="29" t="n">
-        <v>21468.36</v>
+        <v>20952.55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="27" t="n">
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="B14" s="28" t="inlineStr">
         <is>
@@ -2319,12 +2319,12 @@
         </is>
       </c>
       <c r="C14" s="29" t="n">
-        <v>21326.85</v>
+        <v>21464.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="27" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
@@ -2332,12 +2332,12 @@
         </is>
       </c>
       <c r="C15" s="29" t="n">
-        <v>21203.71</v>
+        <v>20629.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="27" t="n">
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="B16" s="28" t="inlineStr">
         <is>
@@ -2345,12 +2345,12 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>21889.32</v>
+        <v>23790.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="27" t="n">
-        <v>46356</v>
+        <v>46363</v>
       </c>
       <c r="B17" s="28" t="inlineStr">
         <is>
@@ -2358,12 +2358,12 @@
         </is>
       </c>
       <c r="C17" s="29" t="n">
-        <v>23828.14</v>
+        <v>23214.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="27" t="n">
-        <v>46363</v>
+        <v>46370</v>
       </c>
       <c r="B18" s="28" t="inlineStr">
         <is>
@@ -2371,12 +2371,12 @@
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>23146.13</v>
+        <v>23268.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="27" t="n">
-        <v>46370</v>
+        <v>46377</v>
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
@@ -2384,12 +2384,12 @@
         </is>
       </c>
       <c r="C19" s="29" t="n">
-        <v>23704.91</v>
+        <v>20933.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="27" t="n">
-        <v>46377</v>
+        <v>46384</v>
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
@@ -2397,12 +2397,12 @@
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>21888.02</v>
+        <v>20028.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="27" t="n">
-        <v>46384</v>
+        <v>46391</v>
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="C21" s="29" t="n">
-        <v>19071.55</v>
+        <v>18936.58</v>
       </c>
     </row>
   </sheetData>
@@ -2667,7 +2667,7 @@
     <row r="6">
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 04 Oct 2026.  Shelly v1.6.0.</t>
+          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 11 Oct 2026.  Shelly v1.19.0.</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 04 Oct 2026 20:46</t>
+          <t>Generated by Shelly on 11 Oct 2026 21:21</t>
         </is>
       </c>
     </row>
